--- a/scheduler/services/resource/data/simulation/telescope_schedules.xlsx
+++ b/scheduler/services/resource/data/simulation/telescope_schedules.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bmiller/python/scheduler/scheduler/services/resource/data/simulation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1168EB76-74D5-D543-844B-368A85520C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE7F8F9F-17AF-C845-847E-856F6431E73D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19500" yWindow="3380" windowWidth="36000" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="3700" windowWidth="36000" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GS" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18988" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21158" uniqueCount="39">
   <si>
     <t>Local Date</t>
   </si>
@@ -445,7 +445,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AD550"/>
+  <dimension ref="A1:AD612"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="8.6640625" customWidth="1"/>
@@ -36253,6 +36253,4346 @@
       <c r="AB550" s="2"/>
       <c r="AC550" s="2"/>
       <c r="AD550" s="2"/>
+    </row>
+    <row r="551" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A551" s="5">
+        <v>46054</v>
+      </c>
+      <c r="B551" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C551" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D551" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E551" s="2"/>
+      <c r="F551" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G551" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H551" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I551" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J551" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K551" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L551" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M551" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N551" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O551" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P551" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q551" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R551" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S551" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T551" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U551" s="2"/>
+      <c r="V551" s="2"/>
+      <c r="W551" s="2"/>
+      <c r="X551" s="2"/>
+      <c r="Y551" s="2"/>
+      <c r="Z551" s="2"/>
+      <c r="AA551" s="2"/>
+      <c r="AB551" s="2"/>
+      <c r="AC551" s="2"/>
+      <c r="AD551" s="2"/>
+    </row>
+    <row r="552" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A552" s="5">
+        <v>46055</v>
+      </c>
+      <c r="B552" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C552" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D552" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E552" s="2"/>
+      <c r="F552" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G552" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H552" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I552" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J552" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K552" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L552" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M552" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N552" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O552" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P552" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q552" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R552" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S552" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T552" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U552" s="2"/>
+      <c r="V552" s="2"/>
+      <c r="W552" s="2"/>
+      <c r="X552" s="2"/>
+      <c r="Y552" s="2"/>
+      <c r="Z552" s="2"/>
+      <c r="AA552" s="2"/>
+      <c r="AB552" s="2"/>
+      <c r="AC552" s="2"/>
+      <c r="AD552" s="2"/>
+    </row>
+    <row r="553" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A553" s="5">
+        <v>46056</v>
+      </c>
+      <c r="B553" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C553" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D553" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E553" s="2"/>
+      <c r="F553" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G553" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H553" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I553" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J553" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K553" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L553" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M553" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N553" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O553" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P553" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q553" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R553" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S553" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T553" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U553" s="2"/>
+      <c r="V553" s="2"/>
+      <c r="W553" s="2"/>
+      <c r="X553" s="2"/>
+      <c r="Y553" s="2"/>
+      <c r="Z553" s="2"/>
+      <c r="AA553" s="2"/>
+      <c r="AB553" s="2"/>
+      <c r="AC553" s="2"/>
+      <c r="AD553" s="2"/>
+    </row>
+    <row r="554" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A554" s="5">
+        <v>46057</v>
+      </c>
+      <c r="B554" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C554" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D554" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E554" s="2"/>
+      <c r="F554" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G554" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H554" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I554" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J554" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K554" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L554" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M554" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N554" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O554" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P554" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q554" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R554" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S554" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T554" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U554" s="2"/>
+      <c r="V554" s="2"/>
+      <c r="W554" s="2"/>
+      <c r="X554" s="2"/>
+      <c r="Y554" s="2"/>
+      <c r="Z554" s="2"/>
+      <c r="AA554" s="2"/>
+      <c r="AB554" s="2"/>
+      <c r="AC554" s="2"/>
+      <c r="AD554" s="2"/>
+    </row>
+    <row r="555" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A555" s="5">
+        <v>46058</v>
+      </c>
+      <c r="B555" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C555" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D555" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E555" s="2"/>
+      <c r="F555" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G555" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H555" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I555" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J555" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K555" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L555" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M555" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N555" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O555" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P555" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q555" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R555" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S555" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T555" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U555" s="2"/>
+      <c r="V555" s="2"/>
+      <c r="W555" s="2"/>
+      <c r="X555" s="2"/>
+      <c r="Y555" s="2"/>
+      <c r="Z555" s="2"/>
+      <c r="AA555" s="2"/>
+      <c r="AB555" s="2"/>
+      <c r="AC555" s="2"/>
+      <c r="AD555" s="2"/>
+    </row>
+    <row r="556" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A556" s="5">
+        <v>46059</v>
+      </c>
+      <c r="B556" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C556" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D556" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E556" s="2"/>
+      <c r="F556" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G556" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H556" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I556" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J556" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K556" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L556" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M556" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N556" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O556" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P556" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q556" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R556" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S556" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T556" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U556" s="2"/>
+      <c r="V556" s="2"/>
+      <c r="W556" s="2"/>
+      <c r="X556" s="2"/>
+      <c r="Y556" s="2"/>
+      <c r="Z556" s="2"/>
+      <c r="AA556" s="2"/>
+      <c r="AB556" s="2"/>
+      <c r="AC556" s="2"/>
+      <c r="AD556" s="2"/>
+    </row>
+    <row r="557" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A557" s="5">
+        <v>46060</v>
+      </c>
+      <c r="B557" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C557" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D557" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E557" s="2"/>
+      <c r="F557" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G557" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H557" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I557" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J557" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K557" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L557" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M557" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N557" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O557" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P557" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q557" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R557" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S557" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T557" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U557" s="2"/>
+      <c r="V557" s="2"/>
+      <c r="W557" s="2"/>
+      <c r="X557" s="2"/>
+      <c r="Y557" s="2"/>
+      <c r="Z557" s="2"/>
+      <c r="AA557" s="2"/>
+      <c r="AB557" s="2"/>
+      <c r="AC557" s="2"/>
+      <c r="AD557" s="2"/>
+    </row>
+    <row r="558" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A558" s="5">
+        <v>46061</v>
+      </c>
+      <c r="B558" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C558" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D558" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E558" s="2"/>
+      <c r="F558" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G558" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H558" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I558" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J558" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K558" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L558" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M558" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N558" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O558" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P558" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q558" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R558" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S558" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T558" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U558" s="2"/>
+      <c r="V558" s="2"/>
+      <c r="W558" s="2"/>
+      <c r="X558" s="2"/>
+      <c r="Y558" s="2"/>
+      <c r="Z558" s="2"/>
+      <c r="AA558" s="2"/>
+      <c r="AB558" s="2"/>
+      <c r="AC558" s="2"/>
+      <c r="AD558" s="2"/>
+    </row>
+    <row r="559" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A559" s="5">
+        <v>46062</v>
+      </c>
+      <c r="B559" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C559" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D559" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E559" s="2"/>
+      <c r="F559" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G559" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H559" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I559" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J559" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K559" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L559" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M559" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N559" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O559" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P559" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q559" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R559" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S559" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T559" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U559" s="2"/>
+      <c r="V559" s="2"/>
+      <c r="W559" s="2"/>
+      <c r="X559" s="2"/>
+      <c r="Y559" s="2"/>
+      <c r="Z559" s="2"/>
+      <c r="AA559" s="2"/>
+      <c r="AB559" s="2"/>
+      <c r="AC559" s="2"/>
+      <c r="AD559" s="2"/>
+    </row>
+    <row r="560" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A560" s="5">
+        <v>46063</v>
+      </c>
+      <c r="B560" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C560" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D560" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E560" s="2"/>
+      <c r="F560" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G560" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H560" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I560" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J560" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K560" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L560" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M560" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N560" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O560" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P560" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q560" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R560" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S560" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T560" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U560" s="2"/>
+      <c r="V560" s="2"/>
+      <c r="W560" s="2"/>
+      <c r="X560" s="2"/>
+      <c r="Y560" s="2"/>
+      <c r="Z560" s="2"/>
+      <c r="AA560" s="2"/>
+      <c r="AB560" s="2"/>
+      <c r="AC560" s="2"/>
+      <c r="AD560" s="2"/>
+    </row>
+    <row r="561" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A561" s="5">
+        <v>46064</v>
+      </c>
+      <c r="B561" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C561" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D561" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E561" s="2"/>
+      <c r="F561" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G561" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H561" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I561" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J561" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K561" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L561" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M561" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N561" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O561" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P561" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q561" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R561" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S561" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T561" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U561" s="2"/>
+      <c r="V561" s="2"/>
+      <c r="W561" s="2"/>
+      <c r="X561" s="2"/>
+      <c r="Y561" s="2"/>
+      <c r="Z561" s="2"/>
+      <c r="AA561" s="2"/>
+      <c r="AB561" s="2"/>
+      <c r="AC561" s="2"/>
+      <c r="AD561" s="2"/>
+    </row>
+    <row r="562" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A562" s="5">
+        <v>46065</v>
+      </c>
+      <c r="B562" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C562" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D562" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E562" s="2"/>
+      <c r="F562" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G562" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H562" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I562" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J562" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K562" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L562" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M562" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N562" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O562" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P562" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q562" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R562" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S562" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T562" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U562" s="2"/>
+      <c r="V562" s="2"/>
+      <c r="W562" s="2"/>
+      <c r="X562" s="2"/>
+      <c r="Y562" s="2"/>
+      <c r="Z562" s="2"/>
+      <c r="AA562" s="2"/>
+      <c r="AB562" s="2"/>
+      <c r="AC562" s="2"/>
+      <c r="AD562" s="2"/>
+    </row>
+    <row r="563" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A563" s="5">
+        <v>46066</v>
+      </c>
+      <c r="B563" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C563" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D563" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E563" s="2"/>
+      <c r="F563" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G563" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H563" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I563" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J563" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K563" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L563" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M563" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N563" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O563" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P563" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q563" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R563" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S563" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T563" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U563" s="2"/>
+      <c r="V563" s="2"/>
+      <c r="W563" s="2"/>
+      <c r="X563" s="2"/>
+      <c r="Y563" s="2"/>
+      <c r="Z563" s="2"/>
+      <c r="AA563" s="2"/>
+      <c r="AB563" s="2"/>
+      <c r="AC563" s="2"/>
+      <c r="AD563" s="2"/>
+    </row>
+    <row r="564" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A564" s="5">
+        <v>46067</v>
+      </c>
+      <c r="B564" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C564" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D564" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E564" s="2"/>
+      <c r="F564" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G564" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H564" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I564" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J564" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K564" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L564" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M564" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N564" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O564" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P564" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q564" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R564" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S564" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T564" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U564" s="2"/>
+      <c r="V564" s="2"/>
+      <c r="W564" s="2"/>
+      <c r="X564" s="2"/>
+      <c r="Y564" s="2"/>
+      <c r="Z564" s="2"/>
+      <c r="AA564" s="2"/>
+      <c r="AB564" s="2"/>
+      <c r="AC564" s="2"/>
+      <c r="AD564" s="2"/>
+    </row>
+    <row r="565" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A565" s="5">
+        <v>46068</v>
+      </c>
+      <c r="B565" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C565" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D565" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E565" s="2"/>
+      <c r="F565" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G565" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H565" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I565" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J565" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K565" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L565" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M565" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N565" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O565" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P565" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q565" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R565" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S565" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T565" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U565" s="2"/>
+      <c r="V565" s="2"/>
+      <c r="W565" s="2"/>
+      <c r="X565" s="2"/>
+      <c r="Y565" s="2"/>
+      <c r="Z565" s="2"/>
+      <c r="AA565" s="2"/>
+      <c r="AB565" s="2"/>
+      <c r="AC565" s="2"/>
+      <c r="AD565" s="2"/>
+    </row>
+    <row r="566" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A566" s="5">
+        <v>46069</v>
+      </c>
+      <c r="B566" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C566" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D566" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E566" s="2"/>
+      <c r="F566" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G566" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H566" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I566" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J566" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K566" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L566" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M566" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N566" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O566" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P566" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q566" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R566" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S566" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T566" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U566" s="2"/>
+      <c r="V566" s="2"/>
+      <c r="W566" s="2"/>
+      <c r="X566" s="2"/>
+      <c r="Y566" s="2"/>
+      <c r="Z566" s="2"/>
+      <c r="AA566" s="2"/>
+      <c r="AB566" s="2"/>
+      <c r="AC566" s="2"/>
+      <c r="AD566" s="2"/>
+    </row>
+    <row r="567" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A567" s="5">
+        <v>46070</v>
+      </c>
+      <c r="B567" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C567" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D567" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E567" s="2"/>
+      <c r="F567" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G567" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H567" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I567" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J567" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K567" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L567" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M567" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N567" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O567" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P567" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q567" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R567" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S567" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T567" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U567" s="2"/>
+      <c r="V567" s="2"/>
+      <c r="W567" s="2"/>
+      <c r="X567" s="2"/>
+      <c r="Y567" s="2"/>
+      <c r="Z567" s="2"/>
+      <c r="AA567" s="2"/>
+      <c r="AB567" s="2"/>
+      <c r="AC567" s="2"/>
+      <c r="AD567" s="2"/>
+    </row>
+    <row r="568" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A568" s="5">
+        <v>46071</v>
+      </c>
+      <c r="B568" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C568" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D568" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E568" s="2"/>
+      <c r="F568" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G568" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H568" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I568" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J568" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K568" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L568" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M568" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N568" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O568" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P568" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q568" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R568" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S568" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T568" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U568" s="2"/>
+      <c r="V568" s="2"/>
+      <c r="W568" s="2"/>
+      <c r="X568" s="2"/>
+      <c r="Y568" s="2"/>
+      <c r="Z568" s="2"/>
+      <c r="AA568" s="2"/>
+      <c r="AB568" s="2"/>
+      <c r="AC568" s="2"/>
+      <c r="AD568" s="2"/>
+    </row>
+    <row r="569" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A569" s="5">
+        <v>46072</v>
+      </c>
+      <c r="B569" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C569" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D569" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E569" s="2"/>
+      <c r="F569" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G569" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H569" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I569" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J569" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K569" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L569" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M569" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N569" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O569" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P569" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q569" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R569" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S569" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T569" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U569" s="2"/>
+      <c r="V569" s="2"/>
+      <c r="W569" s="2"/>
+      <c r="X569" s="2"/>
+      <c r="Y569" s="2"/>
+      <c r="Z569" s="2"/>
+      <c r="AA569" s="2"/>
+      <c r="AB569" s="2"/>
+      <c r="AC569" s="2"/>
+      <c r="AD569" s="2"/>
+    </row>
+    <row r="570" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A570" s="5">
+        <v>46073</v>
+      </c>
+      <c r="B570" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C570" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D570" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E570" s="2"/>
+      <c r="F570" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G570" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H570" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I570" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J570" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K570" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L570" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M570" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N570" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O570" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P570" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q570" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R570" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S570" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T570" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U570" s="2"/>
+      <c r="V570" s="2"/>
+      <c r="W570" s="2"/>
+      <c r="X570" s="2"/>
+      <c r="Y570" s="2"/>
+      <c r="Z570" s="2"/>
+      <c r="AA570" s="2"/>
+      <c r="AB570" s="2"/>
+      <c r="AC570" s="2"/>
+      <c r="AD570" s="2"/>
+    </row>
+    <row r="571" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A571" s="5">
+        <v>46074</v>
+      </c>
+      <c r="B571" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C571" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D571" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E571" s="2"/>
+      <c r="F571" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G571" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H571" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I571" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J571" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K571" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L571" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M571" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N571" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O571" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P571" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q571" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R571" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S571" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T571" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U571" s="2"/>
+      <c r="V571" s="2"/>
+      <c r="W571" s="2"/>
+      <c r="X571" s="2"/>
+      <c r="Y571" s="2"/>
+      <c r="Z571" s="2"/>
+      <c r="AA571" s="2"/>
+      <c r="AB571" s="2"/>
+      <c r="AC571" s="2"/>
+      <c r="AD571" s="2"/>
+    </row>
+    <row r="572" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A572" s="5">
+        <v>46075</v>
+      </c>
+      <c r="B572" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C572" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D572" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E572" s="2"/>
+      <c r="F572" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G572" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H572" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I572" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J572" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K572" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L572" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M572" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N572" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O572" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P572" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q572" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R572" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S572" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T572" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U572" s="2"/>
+      <c r="V572" s="2"/>
+      <c r="W572" s="2"/>
+      <c r="X572" s="2"/>
+      <c r="Y572" s="2"/>
+      <c r="Z572" s="2"/>
+      <c r="AA572" s="2"/>
+      <c r="AB572" s="2"/>
+      <c r="AC572" s="2"/>
+      <c r="AD572" s="2"/>
+    </row>
+    <row r="573" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A573" s="5">
+        <v>46076</v>
+      </c>
+      <c r="B573" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C573" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D573" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E573" s="2"/>
+      <c r="F573" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G573" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H573" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I573" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J573" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K573" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L573" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M573" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N573" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O573" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P573" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q573" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R573" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S573" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T573" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U573" s="2"/>
+      <c r="V573" s="2"/>
+      <c r="W573" s="2"/>
+      <c r="X573" s="2"/>
+      <c r="Y573" s="2"/>
+      <c r="Z573" s="2"/>
+      <c r="AA573" s="2"/>
+      <c r="AB573" s="2"/>
+      <c r="AC573" s="2"/>
+      <c r="AD573" s="2"/>
+    </row>
+    <row r="574" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A574" s="5">
+        <v>46077</v>
+      </c>
+      <c r="B574" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C574" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D574" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E574" s="2"/>
+      <c r="F574" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G574" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H574" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I574" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J574" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K574" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L574" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M574" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N574" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O574" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P574" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q574" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R574" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S574" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T574" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U574" s="2"/>
+      <c r="V574" s="2"/>
+      <c r="W574" s="2"/>
+      <c r="X574" s="2"/>
+      <c r="Y574" s="2"/>
+      <c r="Z574" s="2"/>
+      <c r="AA574" s="2"/>
+      <c r="AB574" s="2"/>
+      <c r="AC574" s="2"/>
+      <c r="AD574" s="2"/>
+    </row>
+    <row r="575" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A575" s="5">
+        <v>46078</v>
+      </c>
+      <c r="B575" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C575" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D575" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E575" s="2"/>
+      <c r="F575" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G575" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H575" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I575" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J575" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K575" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L575" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M575" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N575" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O575" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P575" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q575" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R575" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S575" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T575" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U575" s="2"/>
+      <c r="V575" s="2"/>
+      <c r="W575" s="2"/>
+      <c r="X575" s="2"/>
+      <c r="Y575" s="2"/>
+      <c r="Z575" s="2"/>
+      <c r="AA575" s="2"/>
+      <c r="AB575" s="2"/>
+      <c r="AC575" s="2"/>
+      <c r="AD575" s="2"/>
+    </row>
+    <row r="576" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A576" s="5">
+        <v>46079</v>
+      </c>
+      <c r="B576" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C576" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D576" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E576" s="2"/>
+      <c r="F576" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G576" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H576" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I576" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J576" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K576" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L576" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M576" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N576" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O576" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P576" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q576" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R576" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S576" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T576" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U576" s="2"/>
+      <c r="V576" s="2"/>
+      <c r="W576" s="2"/>
+      <c r="X576" s="2"/>
+      <c r="Y576" s="2"/>
+      <c r="Z576" s="2"/>
+      <c r="AA576" s="2"/>
+      <c r="AB576" s="2"/>
+      <c r="AC576" s="2"/>
+      <c r="AD576" s="2"/>
+    </row>
+    <row r="577" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A577" s="5">
+        <v>46080</v>
+      </c>
+      <c r="B577" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C577" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D577" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E577" s="2"/>
+      <c r="F577" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G577" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H577" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I577" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J577" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K577" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L577" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M577" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N577" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O577" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P577" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q577" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R577" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S577" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T577" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U577" s="2"/>
+      <c r="V577" s="2"/>
+      <c r="W577" s="2"/>
+      <c r="X577" s="2"/>
+      <c r="Y577" s="2"/>
+      <c r="Z577" s="2"/>
+      <c r="AA577" s="2"/>
+      <c r="AB577" s="2"/>
+      <c r="AC577" s="2"/>
+      <c r="AD577" s="2"/>
+    </row>
+    <row r="578" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A578" s="5">
+        <v>46081</v>
+      </c>
+      <c r="B578" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C578" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D578" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E578" s="2"/>
+      <c r="F578" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G578" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H578" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I578" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J578" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K578" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L578" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M578" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N578" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O578" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P578" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q578" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R578" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S578" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T578" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U578" s="2"/>
+      <c r="V578" s="2"/>
+      <c r="W578" s="2"/>
+      <c r="X578" s="2"/>
+      <c r="Y578" s="2"/>
+      <c r="Z578" s="2"/>
+      <c r="AA578" s="2"/>
+      <c r="AB578" s="2"/>
+      <c r="AC578" s="2"/>
+      <c r="AD578" s="2"/>
+    </row>
+    <row r="579" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A579" s="5">
+        <v>46082</v>
+      </c>
+      <c r="B579" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C579" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D579" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E579" s="2"/>
+      <c r="F579" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G579" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H579" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I579" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J579" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K579" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L579" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M579" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N579" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O579" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P579" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q579" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R579" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S579" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T579" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U579" s="2"/>
+      <c r="V579" s="2"/>
+      <c r="W579" s="2"/>
+      <c r="X579" s="2"/>
+      <c r="Y579" s="2"/>
+      <c r="Z579" s="2"/>
+      <c r="AA579" s="2"/>
+      <c r="AB579" s="2"/>
+      <c r="AC579" s="2"/>
+      <c r="AD579" s="2"/>
+    </row>
+    <row r="580" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A580" s="5">
+        <v>46083</v>
+      </c>
+      <c r="B580" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C580" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D580" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E580" s="2"/>
+      <c r="F580" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G580" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H580" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I580" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J580" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K580" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L580" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M580" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N580" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O580" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P580" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q580" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R580" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S580" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T580" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U580" s="2"/>
+      <c r="V580" s="2"/>
+      <c r="W580" s="2"/>
+      <c r="X580" s="2"/>
+      <c r="Y580" s="2"/>
+      <c r="Z580" s="2"/>
+      <c r="AA580" s="2"/>
+      <c r="AB580" s="2"/>
+      <c r="AC580" s="2"/>
+      <c r="AD580" s="2"/>
+    </row>
+    <row r="581" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A581" s="5">
+        <v>46084</v>
+      </c>
+      <c r="B581" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C581" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D581" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E581" s="2"/>
+      <c r="F581" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G581" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H581" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I581" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J581" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K581" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L581" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M581" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N581" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O581" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P581" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q581" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R581" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S581" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T581" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U581" s="2"/>
+      <c r="V581" s="2"/>
+      <c r="W581" s="2"/>
+      <c r="X581" s="2"/>
+      <c r="Y581" s="2"/>
+      <c r="Z581" s="2"/>
+      <c r="AA581" s="2"/>
+      <c r="AB581" s="2"/>
+      <c r="AC581" s="2"/>
+      <c r="AD581" s="2"/>
+    </row>
+    <row r="582" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A582" s="5">
+        <v>46085</v>
+      </c>
+      <c r="B582" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C582" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D582" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E582" s="2"/>
+      <c r="F582" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G582" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H582" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I582" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J582" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K582" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L582" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M582" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N582" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O582" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P582" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q582" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R582" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S582" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T582" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U582" s="2"/>
+      <c r="V582" s="2"/>
+      <c r="W582" s="2"/>
+      <c r="X582" s="2"/>
+      <c r="Y582" s="2"/>
+      <c r="Z582" s="2"/>
+      <c r="AA582" s="2"/>
+      <c r="AB582" s="2"/>
+      <c r="AC582" s="2"/>
+      <c r="AD582" s="2"/>
+    </row>
+    <row r="583" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A583" s="5">
+        <v>46086</v>
+      </c>
+      <c r="B583" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C583" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D583" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E583" s="2"/>
+      <c r="F583" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G583" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H583" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I583" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J583" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K583" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L583" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M583" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N583" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O583" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P583" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q583" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R583" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S583" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T583" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U583" s="2"/>
+      <c r="V583" s="2"/>
+      <c r="W583" s="2"/>
+      <c r="X583" s="2"/>
+      <c r="Y583" s="2"/>
+      <c r="Z583" s="2"/>
+      <c r="AA583" s="2"/>
+      <c r="AB583" s="2"/>
+      <c r="AC583" s="2"/>
+      <c r="AD583" s="2"/>
+    </row>
+    <row r="584" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A584" s="5">
+        <v>46087</v>
+      </c>
+      <c r="B584" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C584" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D584" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E584" s="2"/>
+      <c r="F584" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G584" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H584" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I584" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J584" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K584" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L584" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M584" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N584" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O584" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P584" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q584" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R584" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S584" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T584" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U584" s="2"/>
+      <c r="V584" s="2"/>
+      <c r="W584" s="2"/>
+      <c r="X584" s="2"/>
+      <c r="Y584" s="2"/>
+      <c r="Z584" s="2"/>
+      <c r="AA584" s="2"/>
+      <c r="AB584" s="2"/>
+      <c r="AC584" s="2"/>
+      <c r="AD584" s="2"/>
+    </row>
+    <row r="585" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A585" s="5">
+        <v>46088</v>
+      </c>
+      <c r="B585" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C585" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D585" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E585" s="2"/>
+      <c r="F585" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G585" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H585" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I585" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J585" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K585" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L585" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M585" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N585" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O585" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P585" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q585" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R585" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S585" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T585" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U585" s="2"/>
+      <c r="V585" s="2"/>
+      <c r="W585" s="2"/>
+      <c r="X585" s="2"/>
+      <c r="Y585" s="2"/>
+      <c r="Z585" s="2"/>
+      <c r="AA585" s="2"/>
+      <c r="AB585" s="2"/>
+      <c r="AC585" s="2"/>
+      <c r="AD585" s="2"/>
+    </row>
+    <row r="586" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A586" s="5">
+        <v>46089</v>
+      </c>
+      <c r="B586" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C586" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D586" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E586" s="2"/>
+      <c r="F586" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G586" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H586" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I586" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J586" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K586" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L586" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M586" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N586" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O586" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P586" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q586" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R586" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S586" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T586" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U586" s="2"/>
+      <c r="V586" s="2"/>
+      <c r="W586" s="2"/>
+      <c r="X586" s="2"/>
+      <c r="Y586" s="2"/>
+      <c r="Z586" s="2"/>
+      <c r="AA586" s="2"/>
+      <c r="AB586" s="2"/>
+      <c r="AC586" s="2"/>
+      <c r="AD586" s="2"/>
+    </row>
+    <row r="587" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A587" s="5">
+        <v>46090</v>
+      </c>
+      <c r="B587" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C587" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D587" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E587" s="2"/>
+      <c r="F587" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G587" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H587" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I587" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J587" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K587" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L587" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M587" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N587" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O587" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P587" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q587" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R587" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S587" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T587" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U587" s="2"/>
+      <c r="V587" s="2"/>
+      <c r="W587" s="2"/>
+      <c r="X587" s="2"/>
+      <c r="Y587" s="2"/>
+      <c r="Z587" s="2"/>
+      <c r="AA587" s="2"/>
+      <c r="AB587" s="2"/>
+      <c r="AC587" s="2"/>
+      <c r="AD587" s="2"/>
+    </row>
+    <row r="588" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A588" s="5">
+        <v>46091</v>
+      </c>
+      <c r="B588" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C588" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D588" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E588" s="2"/>
+      <c r="F588" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G588" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H588" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I588" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J588" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K588" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L588" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M588" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N588" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O588" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P588" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q588" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R588" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S588" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T588" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U588" s="2"/>
+      <c r="V588" s="2"/>
+      <c r="W588" s="2"/>
+      <c r="X588" s="2"/>
+      <c r="Y588" s="2"/>
+      <c r="Z588" s="2"/>
+      <c r="AA588" s="2"/>
+      <c r="AB588" s="2"/>
+      <c r="AC588" s="2"/>
+      <c r="AD588" s="2"/>
+    </row>
+    <row r="589" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A589" s="5">
+        <v>46092</v>
+      </c>
+      <c r="B589" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C589" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D589" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E589" s="2"/>
+      <c r="F589" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G589" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H589" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I589" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J589" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K589" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L589" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M589" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N589" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O589" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P589" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q589" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R589" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S589" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T589" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U589" s="2"/>
+      <c r="V589" s="2"/>
+      <c r="W589" s="2"/>
+      <c r="X589" s="2"/>
+      <c r="Y589" s="2"/>
+      <c r="Z589" s="2"/>
+      <c r="AA589" s="2"/>
+      <c r="AB589" s="2"/>
+      <c r="AC589" s="2"/>
+      <c r="AD589" s="2"/>
+    </row>
+    <row r="590" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A590" s="5">
+        <v>46093</v>
+      </c>
+      <c r="B590" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C590" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D590" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E590" s="2"/>
+      <c r="F590" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G590" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H590" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I590" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J590" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K590" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L590" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M590" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N590" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O590" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P590" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q590" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R590" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S590" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T590" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U590" s="2"/>
+      <c r="V590" s="2"/>
+      <c r="W590" s="2"/>
+      <c r="X590" s="2"/>
+      <c r="Y590" s="2"/>
+      <c r="Z590" s="2"/>
+      <c r="AA590" s="2"/>
+      <c r="AB590" s="2"/>
+      <c r="AC590" s="2"/>
+      <c r="AD590" s="2"/>
+    </row>
+    <row r="591" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A591" s="5">
+        <v>46094</v>
+      </c>
+      <c r="B591" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C591" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D591" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E591" s="2"/>
+      <c r="F591" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G591" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H591" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I591" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J591" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K591" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L591" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M591" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N591" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O591" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P591" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q591" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R591" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S591" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T591" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U591" s="2"/>
+      <c r="V591" s="2"/>
+      <c r="W591" s="2"/>
+      <c r="X591" s="2"/>
+      <c r="Y591" s="2"/>
+      <c r="Z591" s="2"/>
+      <c r="AA591" s="2"/>
+      <c r="AB591" s="2"/>
+      <c r="AC591" s="2"/>
+      <c r="AD591" s="2"/>
+    </row>
+    <row r="592" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A592" s="5">
+        <v>46095</v>
+      </c>
+      <c r="B592" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C592" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D592" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E592" s="2"/>
+      <c r="F592" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G592" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H592" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I592" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J592" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K592" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L592" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M592" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N592" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O592" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P592" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q592" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R592" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S592" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T592" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U592" s="2"/>
+      <c r="V592" s="2"/>
+      <c r="W592" s="2"/>
+      <c r="X592" s="2"/>
+      <c r="Y592" s="2"/>
+      <c r="Z592" s="2"/>
+      <c r="AA592" s="2"/>
+      <c r="AB592" s="2"/>
+      <c r="AC592" s="2"/>
+      <c r="AD592" s="2"/>
+    </row>
+    <row r="593" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A593" s="5">
+        <v>46096</v>
+      </c>
+      <c r="B593" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C593" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D593" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E593" s="2"/>
+      <c r="F593" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G593" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H593" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I593" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J593" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K593" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L593" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M593" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N593" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O593" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P593" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q593" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R593" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S593" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T593" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U593" s="2"/>
+      <c r="V593" s="2"/>
+      <c r="W593" s="2"/>
+      <c r="X593" s="2"/>
+      <c r="Y593" s="2"/>
+      <c r="Z593" s="2"/>
+      <c r="AA593" s="2"/>
+      <c r="AB593" s="2"/>
+      <c r="AC593" s="2"/>
+      <c r="AD593" s="2"/>
+    </row>
+    <row r="594" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A594" s="5">
+        <v>46097</v>
+      </c>
+      <c r="B594" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C594" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D594" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E594" s="2"/>
+      <c r="F594" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G594" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H594" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I594" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J594" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K594" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L594" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M594" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N594" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O594" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P594" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q594" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R594" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S594" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T594" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U594" s="2"/>
+      <c r="V594" s="2"/>
+      <c r="W594" s="2"/>
+      <c r="X594" s="2"/>
+      <c r="Y594" s="2"/>
+      <c r="Z594" s="2"/>
+      <c r="AA594" s="2"/>
+      <c r="AB594" s="2"/>
+      <c r="AC594" s="2"/>
+      <c r="AD594" s="2"/>
+    </row>
+    <row r="595" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A595" s="5">
+        <v>46098</v>
+      </c>
+      <c r="B595" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C595" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D595" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E595" s="2"/>
+      <c r="F595" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G595" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H595" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I595" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J595" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K595" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L595" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M595" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N595" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O595" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P595" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q595" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R595" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S595" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T595" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U595" s="2"/>
+      <c r="V595" s="2"/>
+      <c r="W595" s="2"/>
+      <c r="X595" s="2"/>
+      <c r="Y595" s="2"/>
+      <c r="Z595" s="2"/>
+      <c r="AA595" s="2"/>
+      <c r="AB595" s="2"/>
+      <c r="AC595" s="2"/>
+      <c r="AD595" s="2"/>
+    </row>
+    <row r="596" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A596" s="5">
+        <v>46099</v>
+      </c>
+      <c r="B596" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C596" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D596" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E596" s="2"/>
+      <c r="F596" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G596" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H596" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I596" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J596" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K596" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L596" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M596" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N596" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O596" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P596" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q596" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R596" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S596" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T596" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U596" s="2"/>
+      <c r="V596" s="2"/>
+      <c r="W596" s="2"/>
+      <c r="X596" s="2"/>
+      <c r="Y596" s="2"/>
+      <c r="Z596" s="2"/>
+      <c r="AA596" s="2"/>
+      <c r="AB596" s="2"/>
+      <c r="AC596" s="2"/>
+      <c r="AD596" s="2"/>
+    </row>
+    <row r="597" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A597" s="5">
+        <v>46100</v>
+      </c>
+      <c r="B597" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C597" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D597" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E597" s="2"/>
+      <c r="F597" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G597" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H597" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I597" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J597" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K597" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L597" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M597" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N597" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O597" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P597" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q597" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R597" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S597" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T597" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U597" s="2"/>
+      <c r="V597" s="2"/>
+      <c r="W597" s="2"/>
+      <c r="X597" s="2"/>
+      <c r="Y597" s="2"/>
+      <c r="Z597" s="2"/>
+      <c r="AA597" s="2"/>
+      <c r="AB597" s="2"/>
+      <c r="AC597" s="2"/>
+      <c r="AD597" s="2"/>
+    </row>
+    <row r="598" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A598" s="5">
+        <v>46101</v>
+      </c>
+      <c r="B598" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C598" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D598" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E598" s="2"/>
+      <c r="F598" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G598" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H598" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I598" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J598" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K598" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L598" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M598" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N598" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O598" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P598" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q598" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R598" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S598" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T598" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U598" s="2"/>
+      <c r="V598" s="2"/>
+      <c r="W598" s="2"/>
+      <c r="X598" s="2"/>
+      <c r="Y598" s="2"/>
+      <c r="Z598" s="2"/>
+      <c r="AA598" s="2"/>
+      <c r="AB598" s="2"/>
+      <c r="AC598" s="2"/>
+      <c r="AD598" s="2"/>
+    </row>
+    <row r="599" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A599" s="5">
+        <v>46102</v>
+      </c>
+      <c r="B599" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C599" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D599" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E599" s="2"/>
+      <c r="F599" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G599" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H599" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I599" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J599" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K599" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L599" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M599" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N599" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O599" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P599" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q599" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R599" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S599" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T599" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U599" s="2"/>
+      <c r="V599" s="2"/>
+      <c r="W599" s="2"/>
+      <c r="X599" s="2"/>
+      <c r="Y599" s="2"/>
+      <c r="Z599" s="2"/>
+      <c r="AA599" s="2"/>
+      <c r="AB599" s="2"/>
+      <c r="AC599" s="2"/>
+      <c r="AD599" s="2"/>
+    </row>
+    <row r="600" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A600" s="5">
+        <v>46103</v>
+      </c>
+      <c r="B600" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C600" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D600" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E600" s="2"/>
+      <c r="F600" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G600" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H600" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I600" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J600" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K600" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L600" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M600" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N600" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O600" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P600" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q600" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R600" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S600" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T600" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U600" s="2"/>
+      <c r="V600" s="2"/>
+      <c r="W600" s="2"/>
+      <c r="X600" s="2"/>
+      <c r="Y600" s="2"/>
+      <c r="Z600" s="2"/>
+      <c r="AA600" s="2"/>
+      <c r="AB600" s="2"/>
+      <c r="AC600" s="2"/>
+      <c r="AD600" s="2"/>
+    </row>
+    <row r="601" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A601" s="5">
+        <v>46104</v>
+      </c>
+      <c r="B601" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C601" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D601" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E601" s="2"/>
+      <c r="F601" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G601" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H601" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I601" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J601" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K601" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L601" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M601" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N601" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O601" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P601" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q601" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R601" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S601" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T601" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U601" s="2"/>
+      <c r="V601" s="2"/>
+      <c r="W601" s="2"/>
+      <c r="X601" s="2"/>
+      <c r="Y601" s="2"/>
+      <c r="Z601" s="2"/>
+      <c r="AA601" s="2"/>
+      <c r="AB601" s="2"/>
+      <c r="AC601" s="2"/>
+      <c r="AD601" s="2"/>
+    </row>
+    <row r="602" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A602" s="5">
+        <v>46105</v>
+      </c>
+      <c r="B602" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C602" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D602" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E602" s="2"/>
+      <c r="F602" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G602" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H602" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I602" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J602" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K602" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L602" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M602" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N602" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O602" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P602" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q602" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R602" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S602" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T602" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U602" s="2"/>
+      <c r="V602" s="2"/>
+      <c r="W602" s="2"/>
+      <c r="X602" s="2"/>
+      <c r="Y602" s="2"/>
+      <c r="Z602" s="2"/>
+      <c r="AA602" s="2"/>
+      <c r="AB602" s="2"/>
+      <c r="AC602" s="2"/>
+      <c r="AD602" s="2"/>
+    </row>
+    <row r="603" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A603" s="5">
+        <v>46106</v>
+      </c>
+      <c r="B603" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C603" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D603" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E603" s="2"/>
+      <c r="F603" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G603" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H603" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I603" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J603" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K603" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L603" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M603" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N603" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O603" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P603" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q603" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R603" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S603" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T603" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U603" s="2"/>
+      <c r="V603" s="2"/>
+      <c r="W603" s="2"/>
+      <c r="X603" s="2"/>
+      <c r="Y603" s="2"/>
+      <c r="Z603" s="2"/>
+      <c r="AA603" s="2"/>
+      <c r="AB603" s="2"/>
+      <c r="AC603" s="2"/>
+      <c r="AD603" s="2"/>
+    </row>
+    <row r="604" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A604" s="5">
+        <v>46107</v>
+      </c>
+      <c r="B604" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C604" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D604" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E604" s="2"/>
+      <c r="F604" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G604" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H604" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I604" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J604" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K604" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L604" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M604" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N604" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O604" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P604" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q604" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R604" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S604" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T604" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U604" s="2"/>
+      <c r="V604" s="2"/>
+      <c r="W604" s="2"/>
+      <c r="X604" s="2"/>
+      <c r="Y604" s="2"/>
+      <c r="Z604" s="2"/>
+      <c r="AA604" s="2"/>
+      <c r="AB604" s="2"/>
+      <c r="AC604" s="2"/>
+      <c r="AD604" s="2"/>
+    </row>
+    <row r="605" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A605" s="5">
+        <v>46108</v>
+      </c>
+      <c r="B605" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C605" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D605" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E605" s="2"/>
+      <c r="F605" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G605" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H605" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I605" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J605" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K605" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L605" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M605" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N605" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O605" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P605" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q605" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R605" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S605" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T605" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U605" s="2"/>
+      <c r="V605" s="2"/>
+      <c r="W605" s="2"/>
+      <c r="X605" s="2"/>
+      <c r="Y605" s="2"/>
+      <c r="Z605" s="2"/>
+      <c r="AA605" s="2"/>
+      <c r="AB605" s="2"/>
+      <c r="AC605" s="2"/>
+      <c r="AD605" s="2"/>
+    </row>
+    <row r="606" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A606" s="5">
+        <v>46109</v>
+      </c>
+      <c r="B606" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C606" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D606" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E606" s="2"/>
+      <c r="F606" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G606" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H606" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I606" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J606" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K606" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L606" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M606" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N606" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O606" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P606" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q606" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R606" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S606" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T606" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U606" s="2"/>
+      <c r="V606" s="2"/>
+      <c r="W606" s="2"/>
+      <c r="X606" s="2"/>
+      <c r="Y606" s="2"/>
+      <c r="Z606" s="2"/>
+      <c r="AA606" s="2"/>
+      <c r="AB606" s="2"/>
+      <c r="AC606" s="2"/>
+      <c r="AD606" s="2"/>
+    </row>
+    <row r="607" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A607" s="5">
+        <v>46110</v>
+      </c>
+      <c r="B607" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C607" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D607" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E607" s="2"/>
+      <c r="F607" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G607" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H607" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I607" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J607" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K607" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L607" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M607" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N607" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O607" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P607" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q607" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R607" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S607" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T607" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U607" s="2"/>
+      <c r="V607" s="2"/>
+      <c r="W607" s="2"/>
+      <c r="X607" s="2"/>
+      <c r="Y607" s="2"/>
+      <c r="Z607" s="2"/>
+      <c r="AA607" s="2"/>
+      <c r="AB607" s="2"/>
+      <c r="AC607" s="2"/>
+      <c r="AD607" s="2"/>
+    </row>
+    <row r="608" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A608" s="5">
+        <v>46111</v>
+      </c>
+      <c r="B608" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C608" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D608" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E608" s="2"/>
+      <c r="F608" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G608" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H608" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I608" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J608" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K608" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L608" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M608" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N608" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O608" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P608" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q608" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R608" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S608" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T608" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U608" s="2"/>
+      <c r="V608" s="2"/>
+      <c r="W608" s="2"/>
+      <c r="X608" s="2"/>
+      <c r="Y608" s="2"/>
+      <c r="Z608" s="2"/>
+      <c r="AA608" s="2"/>
+      <c r="AB608" s="2"/>
+      <c r="AC608" s="2"/>
+      <c r="AD608" s="2"/>
+    </row>
+    <row r="609" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A609" s="5">
+        <v>46112</v>
+      </c>
+      <c r="B609" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C609" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D609" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E609" s="2"/>
+      <c r="F609" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G609" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H609" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I609" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J609" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K609" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L609" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M609" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N609" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O609" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P609" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q609" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R609" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S609" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T609" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U609" s="2"/>
+      <c r="V609" s="2"/>
+      <c r="W609" s="2"/>
+      <c r="X609" s="2"/>
+      <c r="Y609" s="2"/>
+      <c r="Z609" s="2"/>
+      <c r="AA609" s="2"/>
+      <c r="AB609" s="2"/>
+      <c r="AC609" s="2"/>
+      <c r="AD609" s="2"/>
+    </row>
+    <row r="610" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A610" s="5">
+        <v>46113</v>
+      </c>
+      <c r="B610" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C610" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D610" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E610" s="2"/>
+      <c r="F610" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G610" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H610" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I610" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J610" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K610" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L610" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M610" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N610" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O610" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P610" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q610" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R610" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S610" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T610" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U610" s="2"/>
+      <c r="V610" s="2"/>
+      <c r="W610" s="2"/>
+      <c r="X610" s="2"/>
+      <c r="Y610" s="2"/>
+      <c r="Z610" s="2"/>
+      <c r="AA610" s="2"/>
+      <c r="AB610" s="2"/>
+      <c r="AC610" s="2"/>
+      <c r="AD610" s="2"/>
+    </row>
+    <row r="611" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A611" s="5">
+        <v>46114</v>
+      </c>
+      <c r="B611" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C611" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D611" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E611" s="2"/>
+      <c r="F611" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G611" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H611" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I611" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J611" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K611" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L611" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M611" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N611" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O611" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P611" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q611" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R611" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S611" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T611" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U611" s="2"/>
+      <c r="V611" s="2"/>
+      <c r="W611" s="2"/>
+      <c r="X611" s="2"/>
+      <c r="Y611" s="2"/>
+      <c r="Z611" s="2"/>
+      <c r="AA611" s="2"/>
+      <c r="AB611" s="2"/>
+      <c r="AC611" s="2"/>
+      <c r="AD611" s="2"/>
+    </row>
+    <row r="612" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A612" s="5">
+        <v>46115</v>
+      </c>
+      <c r="B612" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C612" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D612" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E612" s="2"/>
+      <c r="F612" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G612" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H612" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I612" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J612" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K612" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L612" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M612" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N612" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O612" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P612" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q612" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R612" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S612" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T612" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U612" s="2"/>
+      <c r="V612" s="2"/>
+      <c r="W612" s="2"/>
+      <c r="X612" s="2"/>
+      <c r="Y612" s="2"/>
+      <c r="Z612" s="2"/>
+      <c r="AA612" s="2"/>
+      <c r="AB612" s="2"/>
+      <c r="AC612" s="2"/>
+      <c r="AD612" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -36265,7 +40605,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:S550"/>
+  <dimension ref="A1:S612"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="11.6640625" customWidth="1"/>
@@ -67341,6 +71681,3540 @@
         <v>24</v>
       </c>
     </row>
+    <row r="551" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A551" s="5">
+        <v>46054</v>
+      </c>
+      <c r="B551" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C551" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D551" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E551" s="1"/>
+      <c r="F551" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G551" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H551" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I551" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J551" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K551" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L551" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M551" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N551" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O551" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P551" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q551" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R551" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S551" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="552" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A552" s="5">
+        <v>46055</v>
+      </c>
+      <c r="B552" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C552" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D552" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E552" s="1"/>
+      <c r="F552" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G552" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H552" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I552" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J552" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K552" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L552" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M552" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N552" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O552" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P552" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q552" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R552" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S552" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="553" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A553" s="5">
+        <v>46056</v>
+      </c>
+      <c r="B553" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C553" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D553" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E553" s="1"/>
+      <c r="F553" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G553" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H553" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I553" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J553" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K553" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L553" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M553" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N553" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O553" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P553" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q553" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R553" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S553" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="554" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A554" s="5">
+        <v>46057</v>
+      </c>
+      <c r="B554" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C554" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D554" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E554" s="1"/>
+      <c r="F554" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G554" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H554" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I554" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J554" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K554" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L554" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M554" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N554" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O554" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P554" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q554" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R554" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S554" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="555" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A555" s="5">
+        <v>46058</v>
+      </c>
+      <c r="B555" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C555" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D555" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E555" s="1"/>
+      <c r="F555" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G555" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H555" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I555" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J555" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K555" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L555" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M555" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N555" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O555" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P555" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q555" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R555" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S555" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="556" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A556" s="5">
+        <v>46059</v>
+      </c>
+      <c r="B556" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C556" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D556" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E556" s="1"/>
+      <c r="F556" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G556" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H556" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I556" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J556" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K556" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L556" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M556" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N556" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O556" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P556" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q556" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R556" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S556" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="557" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A557" s="5">
+        <v>46060</v>
+      </c>
+      <c r="B557" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C557" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D557" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E557" s="1"/>
+      <c r="F557" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G557" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H557" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I557" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J557" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K557" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L557" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M557" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N557" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O557" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P557" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q557" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R557" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S557" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="558" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A558" s="5">
+        <v>46061</v>
+      </c>
+      <c r="B558" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C558" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D558" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E558" s="1"/>
+      <c r="F558" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G558" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H558" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I558" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J558" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K558" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L558" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M558" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N558" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O558" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P558" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q558" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R558" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S558" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="559" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A559" s="5">
+        <v>46062</v>
+      </c>
+      <c r="B559" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C559" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D559" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E559" s="1"/>
+      <c r="F559" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G559" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H559" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I559" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J559" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K559" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L559" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M559" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N559" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O559" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P559" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q559" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R559" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S559" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="560" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A560" s="5">
+        <v>46063</v>
+      </c>
+      <c r="B560" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C560" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D560" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E560" s="1"/>
+      <c r="F560" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G560" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H560" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I560" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J560" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K560" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L560" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M560" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N560" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O560" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P560" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q560" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R560" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S560" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="561" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A561" s="5">
+        <v>46064</v>
+      </c>
+      <c r="B561" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C561" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D561" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E561" s="1"/>
+      <c r="F561" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G561" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H561" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I561" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J561" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K561" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L561" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M561" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N561" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O561" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P561" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q561" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R561" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S561" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="562" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A562" s="5">
+        <v>46065</v>
+      </c>
+      <c r="B562" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C562" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D562" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E562" s="1"/>
+      <c r="F562" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G562" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H562" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I562" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J562" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K562" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L562" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M562" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N562" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O562" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P562" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q562" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R562" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S562" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="563" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A563" s="5">
+        <v>46066</v>
+      </c>
+      <c r="B563" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C563" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D563" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E563" s="1"/>
+      <c r="F563" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G563" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H563" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I563" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J563" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K563" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L563" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M563" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N563" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O563" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P563" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q563" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R563" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S563" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="564" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A564" s="5">
+        <v>46067</v>
+      </c>
+      <c r="B564" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C564" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D564" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E564" s="1"/>
+      <c r="F564" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G564" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H564" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I564" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J564" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K564" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L564" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M564" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N564" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O564" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P564" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q564" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R564" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S564" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="565" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A565" s="5">
+        <v>46068</v>
+      </c>
+      <c r="B565" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C565" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D565" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E565" s="1"/>
+      <c r="F565" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G565" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H565" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I565" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J565" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K565" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L565" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M565" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N565" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O565" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P565" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q565" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R565" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S565" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="566" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A566" s="5">
+        <v>46069</v>
+      </c>
+      <c r="B566" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C566" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D566" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E566" s="1"/>
+      <c r="F566" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G566" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H566" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I566" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J566" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K566" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L566" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M566" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N566" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O566" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P566" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q566" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R566" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S566" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="567" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A567" s="5">
+        <v>46070</v>
+      </c>
+      <c r="B567" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C567" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D567" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E567" s="1"/>
+      <c r="F567" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G567" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H567" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I567" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J567" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K567" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L567" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M567" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N567" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O567" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P567" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q567" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R567" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S567" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="568" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A568" s="5">
+        <v>46071</v>
+      </c>
+      <c r="B568" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C568" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D568" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E568" s="1"/>
+      <c r="F568" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G568" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H568" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I568" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J568" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K568" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L568" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M568" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N568" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O568" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P568" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q568" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R568" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S568" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="569" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A569" s="5">
+        <v>46072</v>
+      </c>
+      <c r="B569" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C569" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D569" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E569" s="1"/>
+      <c r="F569" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G569" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H569" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I569" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J569" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K569" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L569" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M569" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N569" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O569" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P569" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q569" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R569" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S569" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="570" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A570" s="5">
+        <v>46073</v>
+      </c>
+      <c r="B570" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C570" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D570" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E570" s="1"/>
+      <c r="F570" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G570" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H570" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I570" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J570" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K570" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L570" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M570" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N570" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O570" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P570" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q570" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R570" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S570" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="571" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A571" s="5">
+        <v>46074</v>
+      </c>
+      <c r="B571" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C571" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D571" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E571" s="1"/>
+      <c r="F571" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G571" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H571" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I571" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J571" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K571" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L571" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M571" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N571" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O571" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P571" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q571" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R571" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S571" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="572" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A572" s="5">
+        <v>46075</v>
+      </c>
+      <c r="B572" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C572" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D572" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E572" s="1"/>
+      <c r="F572" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G572" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H572" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I572" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J572" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K572" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L572" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M572" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N572" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O572" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P572" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q572" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R572" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S572" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="573" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A573" s="5">
+        <v>46076</v>
+      </c>
+      <c r="B573" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C573" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D573" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E573" s="1"/>
+      <c r="F573" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G573" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H573" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I573" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J573" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K573" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L573" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M573" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N573" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O573" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P573" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q573" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R573" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S573" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="574" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A574" s="5">
+        <v>46077</v>
+      </c>
+      <c r="B574" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C574" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D574" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E574" s="1"/>
+      <c r="F574" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G574" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H574" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I574" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J574" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K574" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L574" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M574" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N574" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O574" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P574" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q574" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R574" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S574" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="575" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A575" s="5">
+        <v>46078</v>
+      </c>
+      <c r="B575" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C575" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D575" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E575" s="1"/>
+      <c r="F575" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G575" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H575" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I575" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J575" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K575" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L575" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M575" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N575" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O575" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P575" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q575" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R575" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S575" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="576" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A576" s="5">
+        <v>46079</v>
+      </c>
+      <c r="B576" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C576" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D576" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E576" s="1"/>
+      <c r="F576" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G576" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H576" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I576" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J576" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K576" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L576" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M576" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N576" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O576" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P576" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q576" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R576" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S576" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="577" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A577" s="5">
+        <v>46080</v>
+      </c>
+      <c r="B577" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C577" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D577" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E577" s="1"/>
+      <c r="F577" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G577" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H577" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I577" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J577" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K577" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L577" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M577" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N577" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O577" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P577" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q577" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R577" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S577" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="578" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A578" s="5">
+        <v>46081</v>
+      </c>
+      <c r="B578" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C578" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D578" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E578" s="1"/>
+      <c r="F578" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G578" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H578" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I578" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J578" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K578" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L578" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M578" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N578" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O578" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P578" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q578" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R578" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S578" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="579" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A579" s="5">
+        <v>46082</v>
+      </c>
+      <c r="B579" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C579" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D579" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E579" s="1"/>
+      <c r="F579" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G579" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H579" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I579" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J579" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K579" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L579" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M579" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N579" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O579" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P579" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q579" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R579" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S579" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="580" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A580" s="5">
+        <v>46083</v>
+      </c>
+      <c r="B580" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C580" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D580" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E580" s="1"/>
+      <c r="F580" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G580" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H580" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I580" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J580" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K580" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L580" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M580" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N580" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O580" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P580" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q580" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R580" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S580" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="581" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A581" s="5">
+        <v>46084</v>
+      </c>
+      <c r="B581" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C581" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D581" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E581" s="1"/>
+      <c r="F581" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G581" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H581" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I581" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J581" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K581" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L581" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M581" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N581" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O581" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P581" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q581" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R581" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S581" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="582" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A582" s="5">
+        <v>46085</v>
+      </c>
+      <c r="B582" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C582" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D582" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E582" s="1"/>
+      <c r="F582" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G582" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H582" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I582" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J582" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K582" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L582" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M582" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N582" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O582" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P582" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q582" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R582" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S582" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="583" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A583" s="5">
+        <v>46086</v>
+      </c>
+      <c r="B583" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C583" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D583" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E583" s="1"/>
+      <c r="F583" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G583" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H583" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I583" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J583" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K583" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L583" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M583" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N583" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O583" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P583" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q583" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R583" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S583" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="584" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A584" s="5">
+        <v>46087</v>
+      </c>
+      <c r="B584" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C584" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D584" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E584" s="1"/>
+      <c r="F584" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G584" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H584" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I584" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J584" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K584" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L584" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M584" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N584" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O584" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P584" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q584" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R584" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S584" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="585" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A585" s="5">
+        <v>46088</v>
+      </c>
+      <c r="B585" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C585" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D585" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E585" s="1"/>
+      <c r="F585" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G585" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H585" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I585" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J585" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K585" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L585" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M585" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N585" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O585" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P585" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q585" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R585" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S585" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="586" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A586" s="5">
+        <v>46089</v>
+      </c>
+      <c r="B586" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C586" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D586" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E586" s="1"/>
+      <c r="F586" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G586" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H586" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I586" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J586" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K586" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L586" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M586" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N586" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O586" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P586" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q586" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R586" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S586" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="587" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A587" s="5">
+        <v>46090</v>
+      </c>
+      <c r="B587" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C587" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D587" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E587" s="1"/>
+      <c r="F587" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G587" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H587" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I587" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J587" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K587" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L587" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M587" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N587" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O587" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P587" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q587" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R587" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S587" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="588" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A588" s="5">
+        <v>46091</v>
+      </c>
+      <c r="B588" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C588" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D588" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E588" s="1"/>
+      <c r="F588" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G588" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H588" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I588" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J588" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K588" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L588" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M588" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N588" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O588" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P588" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q588" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R588" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S588" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="589" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A589" s="5">
+        <v>46092</v>
+      </c>
+      <c r="B589" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C589" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D589" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E589" s="1"/>
+      <c r="F589" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G589" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H589" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I589" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J589" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K589" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L589" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M589" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N589" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O589" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P589" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q589" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R589" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S589" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="590" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A590" s="5">
+        <v>46093</v>
+      </c>
+      <c r="B590" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C590" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D590" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E590" s="1"/>
+      <c r="F590" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G590" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H590" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I590" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J590" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K590" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L590" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M590" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N590" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O590" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P590" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q590" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R590" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S590" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="591" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A591" s="5">
+        <v>46094</v>
+      </c>
+      <c r="B591" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C591" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D591" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E591" s="1"/>
+      <c r="F591" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G591" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H591" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I591" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J591" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K591" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L591" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M591" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N591" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O591" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P591" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q591" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R591" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S591" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="592" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A592" s="5">
+        <v>46095</v>
+      </c>
+      <c r="B592" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C592" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D592" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E592" s="1"/>
+      <c r="F592" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G592" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H592" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I592" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J592" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K592" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L592" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M592" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N592" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O592" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P592" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q592" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R592" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S592" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="593" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A593" s="5">
+        <v>46096</v>
+      </c>
+      <c r="B593" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C593" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D593" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E593" s="1"/>
+      <c r="F593" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G593" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H593" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I593" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J593" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K593" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L593" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M593" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N593" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O593" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P593" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q593" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R593" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S593" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="594" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A594" s="5">
+        <v>46097</v>
+      </c>
+      <c r="B594" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C594" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D594" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E594" s="1"/>
+      <c r="F594" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G594" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H594" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I594" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J594" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K594" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L594" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M594" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N594" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O594" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P594" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q594" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R594" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S594" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="595" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A595" s="5">
+        <v>46098</v>
+      </c>
+      <c r="B595" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C595" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D595" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E595" s="1"/>
+      <c r="F595" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G595" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H595" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I595" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J595" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K595" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L595" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M595" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N595" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O595" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P595" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q595" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R595" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S595" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="596" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A596" s="5">
+        <v>46099</v>
+      </c>
+      <c r="B596" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C596" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D596" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E596" s="1"/>
+      <c r="F596" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G596" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H596" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I596" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J596" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K596" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L596" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M596" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N596" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O596" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P596" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q596" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R596" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S596" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="597" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A597" s="5">
+        <v>46100</v>
+      </c>
+      <c r="B597" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C597" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D597" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E597" s="1"/>
+      <c r="F597" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G597" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H597" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I597" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J597" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K597" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L597" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M597" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N597" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O597" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P597" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q597" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R597" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S597" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="598" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A598" s="5">
+        <v>46101</v>
+      </c>
+      <c r="B598" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C598" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D598" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E598" s="1"/>
+      <c r="F598" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G598" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H598" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I598" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J598" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K598" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L598" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M598" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N598" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O598" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P598" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q598" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R598" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S598" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="599" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A599" s="5">
+        <v>46102</v>
+      </c>
+      <c r="B599" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C599" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D599" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E599" s="1"/>
+      <c r="F599" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G599" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H599" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I599" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J599" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K599" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L599" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M599" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N599" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O599" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P599" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q599" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R599" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S599" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="600" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A600" s="5">
+        <v>46103</v>
+      </c>
+      <c r="B600" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C600" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D600" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E600" s="1"/>
+      <c r="F600" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G600" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H600" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I600" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J600" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K600" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L600" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M600" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N600" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O600" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P600" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q600" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R600" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S600" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="601" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A601" s="5">
+        <v>46104</v>
+      </c>
+      <c r="B601" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C601" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D601" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E601" s="1"/>
+      <c r="F601" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G601" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H601" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I601" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J601" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K601" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L601" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M601" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N601" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O601" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P601" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q601" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R601" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S601" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="602" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A602" s="5">
+        <v>46105</v>
+      </c>
+      <c r="B602" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C602" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D602" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E602" s="1"/>
+      <c r="F602" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G602" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H602" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I602" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J602" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K602" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L602" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M602" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N602" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O602" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P602" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q602" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R602" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S602" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="603" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A603" s="5">
+        <v>46106</v>
+      </c>
+      <c r="B603" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C603" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D603" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E603" s="1"/>
+      <c r="F603" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G603" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H603" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I603" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J603" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K603" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L603" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M603" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N603" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O603" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P603" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q603" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R603" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S603" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="604" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A604" s="5">
+        <v>46107</v>
+      </c>
+      <c r="B604" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C604" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D604" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E604" s="1"/>
+      <c r="F604" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G604" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H604" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I604" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J604" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K604" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L604" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M604" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N604" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O604" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P604" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q604" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R604" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S604" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="605" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A605" s="5">
+        <v>46108</v>
+      </c>
+      <c r="B605" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C605" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D605" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E605" s="1"/>
+      <c r="F605" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G605" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H605" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I605" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J605" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K605" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L605" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M605" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N605" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O605" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P605" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q605" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R605" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S605" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="606" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A606" s="5">
+        <v>46109</v>
+      </c>
+      <c r="B606" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C606" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D606" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E606" s="1"/>
+      <c r="F606" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G606" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H606" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I606" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J606" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K606" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L606" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M606" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N606" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O606" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P606" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q606" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R606" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S606" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="607" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A607" s="5">
+        <v>46110</v>
+      </c>
+      <c r="B607" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C607" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D607" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E607" s="1"/>
+      <c r="F607" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G607" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H607" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I607" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J607" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K607" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L607" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M607" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N607" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O607" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P607" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q607" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R607" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S607" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="608" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A608" s="5">
+        <v>46111</v>
+      </c>
+      <c r="B608" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C608" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D608" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E608" s="1"/>
+      <c r="F608" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G608" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H608" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I608" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J608" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K608" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L608" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M608" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N608" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O608" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P608" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q608" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R608" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S608" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="609" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A609" s="5">
+        <v>46112</v>
+      </c>
+      <c r="B609" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C609" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D609" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E609" s="1"/>
+      <c r="F609" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G609" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H609" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I609" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J609" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K609" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L609" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M609" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N609" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O609" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P609" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q609" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R609" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S609" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="610" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A610" s="5">
+        <v>46113</v>
+      </c>
+      <c r="B610" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C610" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D610" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E610" s="1"/>
+      <c r="F610" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G610" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H610" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I610" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J610" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K610" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L610" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M610" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N610" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O610" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P610" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q610" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R610" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S610" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="611" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A611" s="5">
+        <v>46114</v>
+      </c>
+      <c r="B611" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C611" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D611" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E611" s="1"/>
+      <c r="F611" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G611" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H611" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I611" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J611" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K611" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L611" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M611" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N611" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O611" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P611" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q611" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R611" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S611" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="612" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A612" s="5">
+        <v>46115</v>
+      </c>
+      <c r="B612" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C612" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D612" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E612" s="1"/>
+      <c r="F612" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G612" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H612" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I612" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J612" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K612" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L612" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M612" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N612" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O612" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P612" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q612" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R612" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S612" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/scheduler/services/resource/data/simulation/telescope_schedules.xlsx
+++ b/scheduler/services/resource/data/simulation/telescope_schedules.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bmiller/python/scheduler/scheduler/services/resource/data/simulation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE7F8F9F-17AF-C845-847E-856F6431E73D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78F0ACF3-54E3-DC49-9E65-BF132583218B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3700" windowWidth="36000" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="3700" windowWidth="36000" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GS" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21158" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22103" uniqueCount="39">
   <si>
     <t>Local Date</t>
   </si>
@@ -445,7 +445,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AD612"/>
+  <dimension ref="A1:AD639"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="8.6640625" customWidth="1"/>
@@ -40593,6 +40593,1896 @@
       <c r="AB612" s="2"/>
       <c r="AC612" s="2"/>
       <c r="AD612" s="2"/>
+    </row>
+    <row r="613" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A613" s="5">
+        <v>46116</v>
+      </c>
+      <c r="B613" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C613" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D613" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E613" s="2"/>
+      <c r="F613" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G613" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H613" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I613" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J613" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K613" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L613" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M613" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N613" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O613" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P613" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q613" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R613" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S613" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T613" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U613" s="2"/>
+      <c r="V613" s="2"/>
+      <c r="W613" s="2"/>
+      <c r="X613" s="2"/>
+      <c r="Y613" s="2"/>
+      <c r="Z613" s="2"/>
+      <c r="AA613" s="2"/>
+      <c r="AB613" s="2"/>
+      <c r="AC613" s="2"/>
+      <c r="AD613" s="2"/>
+    </row>
+    <row r="614" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A614" s="5">
+        <v>46117</v>
+      </c>
+      <c r="B614" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C614" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D614" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E614" s="2"/>
+      <c r="F614" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G614" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H614" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I614" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J614" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K614" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L614" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M614" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N614" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O614" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P614" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q614" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R614" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S614" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T614" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U614" s="2"/>
+      <c r="V614" s="2"/>
+      <c r="W614" s="2"/>
+      <c r="X614" s="2"/>
+      <c r="Y614" s="2"/>
+      <c r="Z614" s="2"/>
+      <c r="AA614" s="2"/>
+      <c r="AB614" s="2"/>
+      <c r="AC614" s="2"/>
+      <c r="AD614" s="2"/>
+    </row>
+    <row r="615" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A615" s="5">
+        <v>46118</v>
+      </c>
+      <c r="B615" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C615" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D615" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E615" s="2"/>
+      <c r="F615" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G615" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H615" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I615" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J615" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K615" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L615" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M615" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N615" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O615" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P615" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q615" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R615" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S615" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T615" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U615" s="2"/>
+      <c r="V615" s="2"/>
+      <c r="W615" s="2"/>
+      <c r="X615" s="2"/>
+      <c r="Y615" s="2"/>
+      <c r="Z615" s="2"/>
+      <c r="AA615" s="2"/>
+      <c r="AB615" s="2"/>
+      <c r="AC615" s="2"/>
+      <c r="AD615" s="2"/>
+    </row>
+    <row r="616" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A616" s="5">
+        <v>46119</v>
+      </c>
+      <c r="B616" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C616" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D616" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E616" s="2"/>
+      <c r="F616" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G616" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H616" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I616" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J616" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K616" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L616" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M616" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N616" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O616" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P616" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q616" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R616" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S616" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T616" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U616" s="2"/>
+      <c r="V616" s="2"/>
+      <c r="W616" s="2"/>
+      <c r="X616" s="2"/>
+      <c r="Y616" s="2"/>
+      <c r="Z616" s="2"/>
+      <c r="AA616" s="2"/>
+      <c r="AB616" s="2"/>
+      <c r="AC616" s="2"/>
+      <c r="AD616" s="2"/>
+    </row>
+    <row r="617" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A617" s="5">
+        <v>46120</v>
+      </c>
+      <c r="B617" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C617" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D617" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E617" s="2"/>
+      <c r="F617" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G617" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H617" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I617" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J617" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K617" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L617" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M617" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N617" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O617" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P617" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q617" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R617" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S617" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T617" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U617" s="2"/>
+      <c r="V617" s="2"/>
+      <c r="W617" s="2"/>
+      <c r="X617" s="2"/>
+      <c r="Y617" s="2"/>
+      <c r="Z617" s="2"/>
+      <c r="AA617" s="2"/>
+      <c r="AB617" s="2"/>
+      <c r="AC617" s="2"/>
+      <c r="AD617" s="2"/>
+    </row>
+    <row r="618" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A618" s="5">
+        <v>46121</v>
+      </c>
+      <c r="B618" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C618" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D618" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E618" s="2"/>
+      <c r="F618" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G618" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H618" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I618" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J618" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K618" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L618" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M618" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N618" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O618" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P618" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q618" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R618" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S618" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T618" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U618" s="2"/>
+      <c r="V618" s="2"/>
+      <c r="W618" s="2"/>
+      <c r="X618" s="2"/>
+      <c r="Y618" s="2"/>
+      <c r="Z618" s="2"/>
+      <c r="AA618" s="2"/>
+      <c r="AB618" s="2"/>
+      <c r="AC618" s="2"/>
+      <c r="AD618" s="2"/>
+    </row>
+    <row r="619" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A619" s="5">
+        <v>46122</v>
+      </c>
+      <c r="B619" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C619" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D619" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E619" s="2"/>
+      <c r="F619" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G619" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H619" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I619" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J619" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K619" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L619" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M619" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N619" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O619" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P619" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q619" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R619" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S619" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T619" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U619" s="2"/>
+      <c r="V619" s="2"/>
+      <c r="W619" s="2"/>
+      <c r="X619" s="2"/>
+      <c r="Y619" s="2"/>
+      <c r="Z619" s="2"/>
+      <c r="AA619" s="2"/>
+      <c r="AB619" s="2"/>
+      <c r="AC619" s="2"/>
+      <c r="AD619" s="2"/>
+    </row>
+    <row r="620" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A620" s="5">
+        <v>46123</v>
+      </c>
+      <c r="B620" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C620" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D620" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E620" s="2"/>
+      <c r="F620" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G620" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H620" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I620" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J620" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K620" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L620" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M620" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N620" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O620" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P620" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q620" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R620" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S620" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T620" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U620" s="2"/>
+      <c r="V620" s="2"/>
+      <c r="W620" s="2"/>
+      <c r="X620" s="2"/>
+      <c r="Y620" s="2"/>
+      <c r="Z620" s="2"/>
+      <c r="AA620" s="2"/>
+      <c r="AB620" s="2"/>
+      <c r="AC620" s="2"/>
+      <c r="AD620" s="2"/>
+    </row>
+    <row r="621" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A621" s="5">
+        <v>46124</v>
+      </c>
+      <c r="B621" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C621" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D621" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E621" s="2"/>
+      <c r="F621" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G621" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H621" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I621" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J621" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K621" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L621" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M621" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N621" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O621" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P621" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q621" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R621" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S621" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T621" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U621" s="2"/>
+      <c r="V621" s="2"/>
+      <c r="W621" s="2"/>
+      <c r="X621" s="2"/>
+      <c r="Y621" s="2"/>
+      <c r="Z621" s="2"/>
+      <c r="AA621" s="2"/>
+      <c r="AB621" s="2"/>
+      <c r="AC621" s="2"/>
+      <c r="AD621" s="2"/>
+    </row>
+    <row r="622" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A622" s="5">
+        <v>46125</v>
+      </c>
+      <c r="B622" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C622" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D622" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E622" s="2"/>
+      <c r="F622" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G622" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H622" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I622" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J622" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K622" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L622" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M622" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N622" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O622" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P622" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q622" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R622" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S622" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T622" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U622" s="2"/>
+      <c r="V622" s="2"/>
+      <c r="W622" s="2"/>
+      <c r="X622" s="2"/>
+      <c r="Y622" s="2"/>
+      <c r="Z622" s="2"/>
+      <c r="AA622" s="2"/>
+      <c r="AB622" s="2"/>
+      <c r="AC622" s="2"/>
+      <c r="AD622" s="2"/>
+    </row>
+    <row r="623" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A623" s="5">
+        <v>46126</v>
+      </c>
+      <c r="B623" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C623" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D623" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E623" s="2"/>
+      <c r="F623" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G623" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H623" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I623" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J623" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K623" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L623" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M623" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N623" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O623" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P623" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q623" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R623" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S623" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T623" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U623" s="2"/>
+      <c r="V623" s="2"/>
+      <c r="W623" s="2"/>
+      <c r="X623" s="2"/>
+      <c r="Y623" s="2"/>
+      <c r="Z623" s="2"/>
+      <c r="AA623" s="2"/>
+      <c r="AB623" s="2"/>
+      <c r="AC623" s="2"/>
+      <c r="AD623" s="2"/>
+    </row>
+    <row r="624" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A624" s="5">
+        <v>46127</v>
+      </c>
+      <c r="B624" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C624" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D624" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E624" s="2"/>
+      <c r="F624" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G624" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H624" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I624" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J624" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K624" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L624" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M624" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N624" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O624" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P624" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q624" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R624" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S624" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T624" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U624" s="2"/>
+      <c r="V624" s="2"/>
+      <c r="W624" s="2"/>
+      <c r="X624" s="2"/>
+      <c r="Y624" s="2"/>
+      <c r="Z624" s="2"/>
+      <c r="AA624" s="2"/>
+      <c r="AB624" s="2"/>
+      <c r="AC624" s="2"/>
+      <c r="AD624" s="2"/>
+    </row>
+    <row r="625" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A625" s="5">
+        <v>46128</v>
+      </c>
+      <c r="B625" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C625" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D625" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E625" s="2"/>
+      <c r="F625" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G625" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H625" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I625" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J625" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K625" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L625" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M625" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N625" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O625" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P625" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q625" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R625" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S625" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T625" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U625" s="2"/>
+      <c r="V625" s="2"/>
+      <c r="W625" s="2"/>
+      <c r="X625" s="2"/>
+      <c r="Y625" s="2"/>
+      <c r="Z625" s="2"/>
+      <c r="AA625" s="2"/>
+      <c r="AB625" s="2"/>
+      <c r="AC625" s="2"/>
+      <c r="AD625" s="2"/>
+    </row>
+    <row r="626" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A626" s="5">
+        <v>46129</v>
+      </c>
+      <c r="B626" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C626" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D626" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E626" s="2"/>
+      <c r="F626" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G626" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H626" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I626" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J626" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K626" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L626" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M626" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N626" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O626" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P626" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q626" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R626" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S626" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T626" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U626" s="2"/>
+      <c r="V626" s="2"/>
+      <c r="W626" s="2"/>
+      <c r="X626" s="2"/>
+      <c r="Y626" s="2"/>
+      <c r="Z626" s="2"/>
+      <c r="AA626" s="2"/>
+      <c r="AB626" s="2"/>
+      <c r="AC626" s="2"/>
+      <c r="AD626" s="2"/>
+    </row>
+    <row r="627" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A627" s="5">
+        <v>46130</v>
+      </c>
+      <c r="B627" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C627" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D627" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E627" s="2"/>
+      <c r="F627" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G627" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H627" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I627" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J627" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K627" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L627" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M627" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N627" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O627" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P627" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q627" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R627" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S627" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T627" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U627" s="2"/>
+      <c r="V627" s="2"/>
+      <c r="W627" s="2"/>
+      <c r="X627" s="2"/>
+      <c r="Y627" s="2"/>
+      <c r="Z627" s="2"/>
+      <c r="AA627" s="2"/>
+      <c r="AB627" s="2"/>
+      <c r="AC627" s="2"/>
+      <c r="AD627" s="2"/>
+    </row>
+    <row r="628" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A628" s="5">
+        <v>46131</v>
+      </c>
+      <c r="B628" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C628" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D628" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E628" s="2"/>
+      <c r="F628" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G628" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H628" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I628" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J628" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K628" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L628" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M628" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N628" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O628" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P628" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q628" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R628" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S628" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T628" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U628" s="2"/>
+      <c r="V628" s="2"/>
+      <c r="W628" s="2"/>
+      <c r="X628" s="2"/>
+      <c r="Y628" s="2"/>
+      <c r="Z628" s="2"/>
+      <c r="AA628" s="2"/>
+      <c r="AB628" s="2"/>
+      <c r="AC628" s="2"/>
+      <c r="AD628" s="2"/>
+    </row>
+    <row r="629" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A629" s="5">
+        <v>46132</v>
+      </c>
+      <c r="B629" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C629" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D629" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E629" s="2"/>
+      <c r="F629" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G629" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H629" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I629" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J629" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K629" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L629" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M629" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N629" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O629" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P629" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q629" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R629" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S629" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T629" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U629" s="2"/>
+      <c r="V629" s="2"/>
+      <c r="W629" s="2"/>
+      <c r="X629" s="2"/>
+      <c r="Y629" s="2"/>
+      <c r="Z629" s="2"/>
+      <c r="AA629" s="2"/>
+      <c r="AB629" s="2"/>
+      <c r="AC629" s="2"/>
+      <c r="AD629" s="2"/>
+    </row>
+    <row r="630" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A630" s="5">
+        <v>46133</v>
+      </c>
+      <c r="B630" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C630" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D630" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E630" s="2"/>
+      <c r="F630" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G630" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H630" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I630" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J630" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K630" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L630" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M630" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N630" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O630" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P630" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q630" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R630" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S630" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T630" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U630" s="2"/>
+      <c r="V630" s="2"/>
+      <c r="W630" s="2"/>
+      <c r="X630" s="2"/>
+      <c r="Y630" s="2"/>
+      <c r="Z630" s="2"/>
+      <c r="AA630" s="2"/>
+      <c r="AB630" s="2"/>
+      <c r="AC630" s="2"/>
+      <c r="AD630" s="2"/>
+    </row>
+    <row r="631" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A631" s="5">
+        <v>46134</v>
+      </c>
+      <c r="B631" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C631" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D631" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E631" s="2"/>
+      <c r="F631" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G631" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H631" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I631" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J631" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K631" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L631" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M631" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N631" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O631" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P631" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q631" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R631" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S631" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T631" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U631" s="2"/>
+      <c r="V631" s="2"/>
+      <c r="W631" s="2"/>
+      <c r="X631" s="2"/>
+      <c r="Y631" s="2"/>
+      <c r="Z631" s="2"/>
+      <c r="AA631" s="2"/>
+      <c r="AB631" s="2"/>
+      <c r="AC631" s="2"/>
+      <c r="AD631" s="2"/>
+    </row>
+    <row r="632" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A632" s="5">
+        <v>46135</v>
+      </c>
+      <c r="B632" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C632" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D632" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E632" s="2"/>
+      <c r="F632" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G632" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H632" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I632" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J632" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K632" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L632" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M632" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N632" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O632" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P632" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q632" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R632" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S632" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T632" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U632" s="2"/>
+      <c r="V632" s="2"/>
+      <c r="W632" s="2"/>
+      <c r="X632" s="2"/>
+      <c r="Y632" s="2"/>
+      <c r="Z632" s="2"/>
+      <c r="AA632" s="2"/>
+      <c r="AB632" s="2"/>
+      <c r="AC632" s="2"/>
+      <c r="AD632" s="2"/>
+    </row>
+    <row r="633" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A633" s="5">
+        <v>46136</v>
+      </c>
+      <c r="B633" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C633" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D633" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E633" s="2"/>
+      <c r="F633" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G633" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H633" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I633" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J633" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K633" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L633" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M633" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N633" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O633" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P633" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q633" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R633" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S633" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T633" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U633" s="2"/>
+      <c r="V633" s="2"/>
+      <c r="W633" s="2"/>
+      <c r="X633" s="2"/>
+      <c r="Y633" s="2"/>
+      <c r="Z633" s="2"/>
+      <c r="AA633" s="2"/>
+      <c r="AB633" s="2"/>
+      <c r="AC633" s="2"/>
+      <c r="AD633" s="2"/>
+    </row>
+    <row r="634" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A634" s="5">
+        <v>46137</v>
+      </c>
+      <c r="B634" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C634" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D634" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E634" s="2"/>
+      <c r="F634" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G634" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H634" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I634" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J634" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K634" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L634" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M634" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N634" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O634" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P634" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q634" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R634" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S634" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T634" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U634" s="2"/>
+      <c r="V634" s="2"/>
+      <c r="W634" s="2"/>
+      <c r="X634" s="2"/>
+      <c r="Y634" s="2"/>
+      <c r="Z634" s="2"/>
+      <c r="AA634" s="2"/>
+      <c r="AB634" s="2"/>
+      <c r="AC634" s="2"/>
+      <c r="AD634" s="2"/>
+    </row>
+    <row r="635" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A635" s="5">
+        <v>46138</v>
+      </c>
+      <c r="B635" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C635" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D635" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E635" s="2"/>
+      <c r="F635" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G635" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H635" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I635" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J635" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K635" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L635" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M635" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N635" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O635" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P635" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q635" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R635" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S635" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T635" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U635" s="2"/>
+      <c r="V635" s="2"/>
+      <c r="W635" s="2"/>
+      <c r="X635" s="2"/>
+      <c r="Y635" s="2"/>
+      <c r="Z635" s="2"/>
+      <c r="AA635" s="2"/>
+      <c r="AB635" s="2"/>
+      <c r="AC635" s="2"/>
+      <c r="AD635" s="2"/>
+    </row>
+    <row r="636" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A636" s="5">
+        <v>46139</v>
+      </c>
+      <c r="B636" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C636" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D636" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E636" s="2"/>
+      <c r="F636" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G636" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H636" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I636" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J636" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K636" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L636" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M636" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N636" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O636" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P636" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q636" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R636" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S636" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T636" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U636" s="2"/>
+      <c r="V636" s="2"/>
+      <c r="W636" s="2"/>
+      <c r="X636" s="2"/>
+      <c r="Y636" s="2"/>
+      <c r="Z636" s="2"/>
+      <c r="AA636" s="2"/>
+      <c r="AB636" s="2"/>
+      <c r="AC636" s="2"/>
+      <c r="AD636" s="2"/>
+    </row>
+    <row r="637" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A637" s="5">
+        <v>46140</v>
+      </c>
+      <c r="B637" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C637" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D637" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E637" s="2"/>
+      <c r="F637" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G637" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H637" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I637" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J637" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K637" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L637" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M637" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N637" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O637" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P637" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q637" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R637" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S637" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T637" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U637" s="2"/>
+      <c r="V637" s="2"/>
+      <c r="W637" s="2"/>
+      <c r="X637" s="2"/>
+      <c r="Y637" s="2"/>
+      <c r="Z637" s="2"/>
+      <c r="AA637" s="2"/>
+      <c r="AB637" s="2"/>
+      <c r="AC637" s="2"/>
+      <c r="AD637" s="2"/>
+    </row>
+    <row r="638" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A638" s="5">
+        <v>46141</v>
+      </c>
+      <c r="B638" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C638" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D638" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E638" s="2"/>
+      <c r="F638" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G638" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H638" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I638" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J638" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K638" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L638" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M638" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N638" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O638" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P638" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q638" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R638" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S638" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T638" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U638" s="2"/>
+      <c r="V638" s="2"/>
+      <c r="W638" s="2"/>
+      <c r="X638" s="2"/>
+      <c r="Y638" s="2"/>
+      <c r="Z638" s="2"/>
+      <c r="AA638" s="2"/>
+      <c r="AB638" s="2"/>
+      <c r="AC638" s="2"/>
+      <c r="AD638" s="2"/>
+    </row>
+    <row r="639" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="A639" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B639" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C639" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D639" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E639" s="2"/>
+      <c r="F639" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G639" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H639" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I639" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J639" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K639" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L639" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M639" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N639" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O639" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P639" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q639" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R639" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S639" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T639" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U639" s="2"/>
+      <c r="V639" s="2"/>
+      <c r="W639" s="2"/>
+      <c r="X639" s="2"/>
+      <c r="Y639" s="2"/>
+      <c r="Z639" s="2"/>
+      <c r="AA639" s="2"/>
+      <c r="AB639" s="2"/>
+      <c r="AC639" s="2"/>
+      <c r="AD639" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -40605,7 +42495,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:S612"/>
+  <dimension ref="A1:S639"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="11.6640625" customWidth="1"/>
@@ -75215,6 +77105,1545 @@
         <v>24</v>
       </c>
     </row>
+    <row r="613" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A613" s="5">
+        <v>46116</v>
+      </c>
+      <c r="B613" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C613" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D613" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E613" s="1"/>
+      <c r="F613" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G613" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H613" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I613" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J613" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K613" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L613" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M613" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N613" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O613" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P613" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q613" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R613" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S613" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="614" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A614" s="5">
+        <v>46117</v>
+      </c>
+      <c r="B614" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C614" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D614" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E614" s="1"/>
+      <c r="F614" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G614" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H614" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I614" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J614" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K614" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L614" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M614" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N614" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O614" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P614" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q614" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R614" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S614" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="615" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A615" s="5">
+        <v>46118</v>
+      </c>
+      <c r="B615" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C615" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D615" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E615" s="1"/>
+      <c r="F615" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G615" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H615" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I615" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J615" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K615" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L615" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M615" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N615" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O615" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P615" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q615" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R615" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S615" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="616" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A616" s="5">
+        <v>46119</v>
+      </c>
+      <c r="B616" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C616" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D616" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E616" s="1"/>
+      <c r="F616" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G616" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H616" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I616" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J616" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K616" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L616" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M616" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N616" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O616" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P616" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q616" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R616" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S616" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="617" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A617" s="5">
+        <v>46120</v>
+      </c>
+      <c r="B617" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C617" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D617" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E617" s="1"/>
+      <c r="F617" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G617" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H617" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I617" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J617" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K617" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L617" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M617" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N617" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O617" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P617" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q617" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R617" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S617" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="618" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A618" s="5">
+        <v>46121</v>
+      </c>
+      <c r="B618" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C618" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D618" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E618" s="1"/>
+      <c r="F618" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G618" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H618" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I618" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J618" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K618" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L618" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M618" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N618" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O618" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P618" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q618" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R618" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S618" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="619" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A619" s="5">
+        <v>46122</v>
+      </c>
+      <c r="B619" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C619" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D619" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E619" s="1"/>
+      <c r="F619" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G619" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H619" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I619" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J619" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K619" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L619" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M619" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N619" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O619" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P619" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q619" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R619" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S619" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="620" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A620" s="5">
+        <v>46123</v>
+      </c>
+      <c r="B620" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C620" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D620" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E620" s="1"/>
+      <c r="F620" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G620" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H620" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I620" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J620" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K620" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L620" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M620" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N620" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O620" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P620" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q620" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R620" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S620" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="621" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A621" s="5">
+        <v>46124</v>
+      </c>
+      <c r="B621" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C621" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D621" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E621" s="1"/>
+      <c r="F621" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G621" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H621" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I621" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J621" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K621" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L621" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M621" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N621" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O621" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P621" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q621" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R621" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S621" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="622" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A622" s="5">
+        <v>46125</v>
+      </c>
+      <c r="B622" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C622" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D622" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E622" s="1"/>
+      <c r="F622" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G622" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H622" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I622" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J622" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K622" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L622" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M622" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N622" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O622" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P622" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q622" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R622" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S622" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="623" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A623" s="5">
+        <v>46126</v>
+      </c>
+      <c r="B623" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C623" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D623" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E623" s="1"/>
+      <c r="F623" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G623" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H623" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I623" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J623" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K623" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L623" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M623" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N623" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O623" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P623" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q623" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R623" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S623" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="624" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A624" s="5">
+        <v>46127</v>
+      </c>
+      <c r="B624" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C624" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D624" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E624" s="1"/>
+      <c r="F624" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G624" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H624" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I624" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J624" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K624" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L624" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M624" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N624" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O624" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P624" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q624" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R624" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S624" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="625" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A625" s="5">
+        <v>46128</v>
+      </c>
+      <c r="B625" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C625" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D625" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E625" s="1"/>
+      <c r="F625" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G625" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H625" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I625" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J625" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K625" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L625" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M625" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N625" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O625" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P625" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q625" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R625" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S625" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="626" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A626" s="5">
+        <v>46129</v>
+      </c>
+      <c r="B626" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C626" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D626" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E626" s="1"/>
+      <c r="F626" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G626" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H626" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I626" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J626" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K626" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L626" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M626" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N626" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O626" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P626" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q626" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R626" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S626" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="627" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A627" s="5">
+        <v>46130</v>
+      </c>
+      <c r="B627" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C627" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D627" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E627" s="1"/>
+      <c r="F627" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G627" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H627" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I627" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J627" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K627" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L627" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M627" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N627" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O627" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P627" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q627" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R627" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S627" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="628" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A628" s="5">
+        <v>46131</v>
+      </c>
+      <c r="B628" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C628" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D628" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E628" s="1"/>
+      <c r="F628" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G628" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H628" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I628" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J628" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K628" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L628" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M628" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N628" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O628" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P628" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q628" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R628" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S628" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="629" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A629" s="5">
+        <v>46132</v>
+      </c>
+      <c r="B629" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C629" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D629" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E629" s="1"/>
+      <c r="F629" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G629" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H629" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I629" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J629" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K629" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L629" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M629" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N629" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O629" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P629" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q629" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R629" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S629" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="630" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A630" s="5">
+        <v>46133</v>
+      </c>
+      <c r="B630" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C630" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D630" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E630" s="1"/>
+      <c r="F630" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G630" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H630" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I630" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J630" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K630" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L630" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M630" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N630" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O630" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P630" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q630" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R630" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S630" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="631" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A631" s="5">
+        <v>46134</v>
+      </c>
+      <c r="B631" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C631" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D631" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E631" s="1"/>
+      <c r="F631" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G631" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H631" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I631" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J631" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K631" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L631" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M631" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N631" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O631" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P631" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q631" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R631" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S631" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="632" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A632" s="5">
+        <v>46135</v>
+      </c>
+      <c r="B632" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C632" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D632" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E632" s="1"/>
+      <c r="F632" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G632" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H632" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I632" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J632" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K632" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L632" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M632" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N632" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O632" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P632" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q632" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R632" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S632" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="633" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A633" s="5">
+        <v>46136</v>
+      </c>
+      <c r="B633" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C633" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D633" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E633" s="1"/>
+      <c r="F633" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G633" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H633" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I633" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J633" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K633" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L633" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M633" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N633" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O633" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P633" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q633" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R633" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S633" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="634" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A634" s="5">
+        <v>46137</v>
+      </c>
+      <c r="B634" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C634" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D634" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E634" s="1"/>
+      <c r="F634" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G634" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H634" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I634" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J634" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K634" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L634" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M634" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N634" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O634" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P634" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q634" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R634" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S634" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="635" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A635" s="5">
+        <v>46138</v>
+      </c>
+      <c r="B635" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C635" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D635" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E635" s="1"/>
+      <c r="F635" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G635" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H635" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I635" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J635" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K635" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L635" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M635" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N635" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O635" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P635" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q635" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R635" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S635" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="636" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A636" s="5">
+        <v>46139</v>
+      </c>
+      <c r="B636" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C636" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D636" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E636" s="1"/>
+      <c r="F636" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G636" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H636" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I636" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J636" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K636" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L636" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M636" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N636" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O636" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P636" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q636" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R636" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S636" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="637" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A637" s="5">
+        <v>46140</v>
+      </c>
+      <c r="B637" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C637" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D637" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E637" s="1"/>
+      <c r="F637" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G637" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H637" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I637" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J637" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K637" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L637" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M637" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N637" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O637" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P637" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q637" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R637" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S637" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="638" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A638" s="5">
+        <v>46141</v>
+      </c>
+      <c r="B638" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C638" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D638" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E638" s="1"/>
+      <c r="F638" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G638" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H638" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I638" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J638" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K638" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L638" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M638" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N638" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O638" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P638" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q638" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R638" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S638" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="639" spans="1:19" ht="13" x14ac:dyDescent="0.15">
+      <c r="A639" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B639" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C639" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D639" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E639" s="1"/>
+      <c r="F639" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G639" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H639" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I639" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J639" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K639" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L639" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M639" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N639" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O639" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P639" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q639" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R639" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S639" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
